--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -831,7 +831,13 @@
           <t>12/09/2026</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="n"/>
+      <c r="Q1" s="23" t="n"/>
+      <c r="R1" s="17" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="S1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -915,6 +921,16 @@
         </is>
       </c>
       <c r="Q2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="R2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="S2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -978,6 +994,12 @@
       <c r="Q3" s="22" t="n">
         <v>4703</v>
       </c>
+      <c r="R3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S3" s="22" t="n">
+        <v>4705</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1037,6 +1059,12 @@
       <c r="Q4" s="22" t="n">
         <v>15644</v>
       </c>
+      <c r="R4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S4" s="22" t="n">
+        <v>15653</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1096,6 +1124,12 @@
       <c r="Q5" s="22" t="n">
         <v>5093</v>
       </c>
+      <c r="R5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S5" s="22" t="n">
+        <v>5107</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1155,6 +1189,12 @@
       <c r="Q6" s="22" t="n">
         <v>6410</v>
       </c>
+      <c r="R6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S6" s="22" t="n">
+        <v>6417</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1214,6 +1254,12 @@
       <c r="Q7" s="22" t="n">
         <v>2190</v>
       </c>
+      <c r="R7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S7" s="22" t="n">
+        <v>2192</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1273,6 +1319,12 @@
       <c r="Q8" s="22" t="n">
         <v>7112</v>
       </c>
+      <c r="R8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S8" s="22" t="n">
+        <v>7121</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1332,6 +1384,12 @@
       <c r="Q9" s="22" t="n">
         <v>3593</v>
       </c>
+      <c r="R9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S9" s="22" t="n">
+        <v>3599</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1391,6 +1449,12 @@
       <c r="Q10" s="22" t="n">
         <v>2649</v>
       </c>
+      <c r="R10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S10" s="22" t="n">
+        <v>2654</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1450,6 +1514,12 @@
       <c r="Q11" s="22" t="n">
         <v>919</v>
       </c>
+      <c r="R11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S11" s="22" t="n">
+        <v>918</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1509,6 +1579,12 @@
       <c r="Q12" s="22" t="n">
         <v>1098</v>
       </c>
+      <c r="R12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S12" s="22" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1568,6 +1644,12 @@
       <c r="Q13" s="22" t="n">
         <v>2055</v>
       </c>
+      <c r="R13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S13" s="22" t="n">
+        <v>2083</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1627,6 +1709,12 @@
       <c r="Q14" s="22" t="n">
         <v>2275</v>
       </c>
+      <c r="R14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S14" s="22" t="n">
+        <v>2282</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1686,6 +1774,12 @@
       <c r="Q15" s="22" t="n">
         <v>2440</v>
       </c>
+      <c r="R15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S15" s="22" t="n">
+        <v>2455</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1745,6 +1839,12 @@
       <c r="Q16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="R16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S16" s="22" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1804,6 +1904,12 @@
       <c r="Q17" s="22" t="n">
         <v>1220</v>
       </c>
+      <c r="R17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S17" s="22" t="n">
+        <v>1223</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1863,6 +1969,12 @@
       <c r="Q18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="R18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -1922,6 +2034,12 @@
       <c r="Q19" s="22" t="n">
         <v>851</v>
       </c>
+      <c r="R19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S19" s="22" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -1981,6 +2099,12 @@
       <c r="Q20" s="22" t="n">
         <v>1022</v>
       </c>
+      <c r="R20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S20" s="22" t="n">
+        <v>1025</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2040,6 +2164,12 @@
       <c r="Q21" s="22" t="n">
         <v>722</v>
       </c>
+      <c r="R21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S21" s="22" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2099,6 +2229,12 @@
       <c r="Q22" s="22" t="n">
         <v>583</v>
       </c>
+      <c r="R22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S22" s="22" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2158,6 +2294,12 @@
       <c r="Q23" s="22" t="n">
         <v>722</v>
       </c>
+      <c r="R23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S23" s="22" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2217,6 +2359,12 @@
       <c r="Q24" s="22" t="n">
         <v>1403</v>
       </c>
+      <c r="R24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S24" s="22" t="n">
+        <v>1402</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2276,6 +2424,12 @@
       <c r="Q25" s="22" t="n">
         <v>562</v>
       </c>
+      <c r="R25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S25" s="22" t="n">
+        <v>568</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2335,9 +2489,15 @@
       <c r="Q26" s="22" t="n">
         <v>251</v>
       </c>
+      <c r="R26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S26" s="22" t="n">
+        <v>252</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="L1:M1"/>
@@ -2345,6 +2505,7 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -837,7 +837,13 @@
           <t>13/09/2026</t>
         </is>
       </c>
-      <c r="S1" s="18" t="n"/>
+      <c r="S1" s="23" t="n"/>
+      <c r="T1" s="17" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="U1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -931,6 +937,16 @@
         </is>
       </c>
       <c r="S2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="T2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="U2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1000,6 +1016,12 @@
       <c r="S3" s="22" t="n">
         <v>4705</v>
       </c>
+      <c r="T3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U3" s="22" t="n">
+        <v>4708</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1065,6 +1087,12 @@
       <c r="S4" s="22" t="n">
         <v>15653</v>
       </c>
+      <c r="T4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U4" s="22" t="n">
+        <v>15654</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1130,6 +1158,12 @@
       <c r="S5" s="22" t="n">
         <v>5107</v>
       </c>
+      <c r="T5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U5" s="22" t="n">
+        <v>5123</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1195,6 +1229,12 @@
       <c r="S6" s="22" t="n">
         <v>6417</v>
       </c>
+      <c r="T6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U6" s="22" t="n">
+        <v>6427</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1260,6 +1300,12 @@
       <c r="S7" s="22" t="n">
         <v>2192</v>
       </c>
+      <c r="T7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U7" s="22" t="n">
+        <v>2201</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1325,6 +1371,12 @@
       <c r="S8" s="22" t="n">
         <v>7121</v>
       </c>
+      <c r="T8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U8" s="22" t="n">
+        <v>7124</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1390,6 +1442,12 @@
       <c r="S9" s="22" t="n">
         <v>3599</v>
       </c>
+      <c r="T9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U9" s="22" t="n">
+        <v>3598</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1455,6 +1513,12 @@
       <c r="S10" s="22" t="n">
         <v>2654</v>
       </c>
+      <c r="T10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U10" s="22" t="n">
+        <v>2661</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1520,6 +1584,12 @@
       <c r="S11" s="22" t="n">
         <v>918</v>
       </c>
+      <c r="T11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U11" s="22" t="n">
+        <v>925</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1585,6 +1655,12 @@
       <c r="S12" s="22" t="n">
         <v>1098</v>
       </c>
+      <c r="T12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U12" s="22" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1650,6 +1726,12 @@
       <c r="S13" s="22" t="n">
         <v>2083</v>
       </c>
+      <c r="T13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U13" s="22" t="n">
+        <v>2072</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1715,6 +1797,12 @@
       <c r="S14" s="22" t="n">
         <v>2282</v>
       </c>
+      <c r="T14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U14" s="22" t="n">
+        <v>2296</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1780,6 +1868,12 @@
       <c r="S15" s="22" t="n">
         <v>2455</v>
       </c>
+      <c r="T15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U15" s="22" t="n">
+        <v>2462</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1845,6 +1939,12 @@
       <c r="S16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="T16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U16" s="22" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1910,6 +2010,12 @@
       <c r="S17" s="22" t="n">
         <v>1223</v>
       </c>
+      <c r="T17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U17" s="22" t="n">
+        <v>1229</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1975,6 +2081,12 @@
       <c r="S18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="T18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2040,6 +2152,12 @@
       <c r="S19" s="22" t="n">
         <v>851</v>
       </c>
+      <c r="T19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U19" s="22" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2105,6 +2223,12 @@
       <c r="S20" s="22" t="n">
         <v>1025</v>
       </c>
+      <c r="T20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U20" s="22" t="n">
+        <v>1030</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2170,6 +2294,12 @@
       <c r="S21" s="22" t="n">
         <v>722</v>
       </c>
+      <c r="T21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U21" s="22" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2235,6 +2365,12 @@
       <c r="S22" s="22" t="n">
         <v>585</v>
       </c>
+      <c r="T22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U22" s="22" t="n">
+        <v>589</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2300,6 +2436,12 @@
       <c r="S23" s="22" t="n">
         <v>722</v>
       </c>
+      <c r="T23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U23" s="22" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2365,6 +2507,12 @@
       <c r="S24" s="22" t="n">
         <v>1402</v>
       </c>
+      <c r="T24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U24" s="22" t="n">
+        <v>1403</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2430,6 +2578,12 @@
       <c r="S25" s="22" t="n">
         <v>568</v>
       </c>
+      <c r="T25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U25" s="22" t="n">
+        <v>572</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2495,10 +2649,17 @@
       <c r="S26" s="22" t="n">
         <v>252</v>
       </c>
+      <c r="T26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U26" s="22" t="n">
+        <v>253</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -843,7 +843,13 @@
           <t>14/09/2026</t>
         </is>
       </c>
-      <c r="U1" s="18" t="n"/>
+      <c r="U1" s="23" t="n"/>
+      <c r="V1" s="17" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="W1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -947,6 +953,16 @@
         </is>
       </c>
       <c r="U2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="V2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="W2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1022,6 +1038,12 @@
       <c r="U3" s="22" t="n">
         <v>4708</v>
       </c>
+      <c r="V3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W3" s="22" t="n">
+        <v>4708</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1093,6 +1115,12 @@
       <c r="U4" s="22" t="n">
         <v>15654</v>
       </c>
+      <c r="V4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W4" s="22" t="n">
+        <v>15661</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1164,6 +1192,12 @@
       <c r="U5" s="22" t="n">
         <v>5123</v>
       </c>
+      <c r="V5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W5" s="22" t="n">
+        <v>5133</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1235,6 +1269,12 @@
       <c r="U6" s="22" t="n">
         <v>6427</v>
       </c>
+      <c r="V6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W6" s="22" t="n">
+        <v>6432</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1306,6 +1346,12 @@
       <c r="U7" s="22" t="n">
         <v>2201</v>
       </c>
+      <c r="V7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W7" s="22" t="n">
+        <v>2196</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1377,6 +1423,12 @@
       <c r="U8" s="22" t="n">
         <v>7124</v>
       </c>
+      <c r="V8" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W8" s="22" t="n">
+        <v>7119</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1448,6 +1500,12 @@
       <c r="U9" s="22" t="n">
         <v>3598</v>
       </c>
+      <c r="V9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W9" s="22" t="n">
+        <v>3596</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1519,6 +1577,12 @@
       <c r="U10" s="22" t="n">
         <v>2661</v>
       </c>
+      <c r="V10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W10" s="22" t="n">
+        <v>2668</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1590,6 +1654,12 @@
       <c r="U11" s="22" t="n">
         <v>925</v>
       </c>
+      <c r="V11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W11" s="22" t="n">
+        <v>942</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1661,6 +1731,12 @@
       <c r="U12" s="22" t="n">
         <v>1094</v>
       </c>
+      <c r="V12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" s="22" t="n">
+        <v>1095</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1732,6 +1808,12 @@
       <c r="U13" s="22" t="n">
         <v>2072</v>
       </c>
+      <c r="V13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W13" s="22" t="n">
+        <v>2081</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1803,6 +1885,12 @@
       <c r="U14" s="22" t="n">
         <v>2296</v>
       </c>
+      <c r="V14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W14" s="22" t="n">
+        <v>2303</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1874,6 +1962,12 @@
       <c r="U15" s="22" t="n">
         <v>2462</v>
       </c>
+      <c r="V15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W15" s="22" t="n">
+        <v>2472</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1945,6 +2039,12 @@
       <c r="U16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="V16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W16" s="22" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2016,6 +2116,12 @@
       <c r="U17" s="22" t="n">
         <v>1229</v>
       </c>
+      <c r="V17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W17" s="22" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2087,6 +2193,12 @@
       <c r="U18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="V18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2158,6 +2270,12 @@
       <c r="U19" s="22" t="n">
         <v>855</v>
       </c>
+      <c r="V19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W19" s="22" t="n">
+        <v>858</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2229,6 +2347,12 @@
       <c r="U20" s="22" t="n">
         <v>1030</v>
       </c>
+      <c r="V20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W20" s="22" t="n">
+        <v>1034</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2300,6 +2424,12 @@
       <c r="U21" s="22" t="n">
         <v>722</v>
       </c>
+      <c r="V21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W21" s="22" t="n">
+        <v>725</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2371,6 +2501,12 @@
       <c r="U22" s="22" t="n">
         <v>589</v>
       </c>
+      <c r="V22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W22" s="22" t="n">
+        <v>590</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2442,6 +2578,12 @@
       <c r="U23" s="22" t="n">
         <v>722</v>
       </c>
+      <c r="V23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W23" s="22" t="n">
+        <v>725</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2513,6 +2655,12 @@
       <c r="U24" s="22" t="n">
         <v>1403</v>
       </c>
+      <c r="V24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W24" s="22" t="n">
+        <v>1405</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2584,6 +2732,12 @@
       <c r="U25" s="22" t="n">
         <v>572</v>
       </c>
+      <c r="V25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="W25" s="22" t="n">
+        <v>573</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2655,10 +2809,17 @@
       <c r="U26" s="22" t="n">
         <v>253</v>
       </c>
+      <c r="V26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W26" s="22" t="n">
+        <v>257</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="L1:M1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -849,7 +849,13 @@
           <t>15/09/2026</t>
         </is>
       </c>
-      <c r="W1" s="18" t="n"/>
+      <c r="W1" s="23" t="n"/>
+      <c r="X1" s="17" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="Y1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -963,6 +969,16 @@
         </is>
       </c>
       <c r="W2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="X2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="Y2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1044,6 +1060,8 @@
       <c r="W3" s="22" t="n">
         <v>4708</v>
       </c>
+      <c r="X3" s="21" t="n"/>
+      <c r="Y3" s="22" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1121,6 +1139,12 @@
       <c r="W4" s="22" t="n">
         <v>15661</v>
       </c>
+      <c r="X4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y4" s="22" t="n">
+        <v>15664</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1198,6 +1222,12 @@
       <c r="W5" s="22" t="n">
         <v>5133</v>
       </c>
+      <c r="X5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y5" s="22" t="n">
+        <v>5150</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1275,6 +1305,12 @@
       <c r="W6" s="22" t="n">
         <v>6432</v>
       </c>
+      <c r="X6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y6" s="22" t="n">
+        <v>6439</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1352,6 +1388,12 @@
       <c r="W7" s="22" t="n">
         <v>2196</v>
       </c>
+      <c r="X7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y7" s="22" t="n">
+        <v>2202</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1429,6 +1471,12 @@
       <c r="W8" s="22" t="n">
         <v>7119</v>
       </c>
+      <c r="X8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y8" s="22" t="n">
+        <v>7127</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1506,6 +1554,12 @@
       <c r="W9" s="22" t="n">
         <v>3596</v>
       </c>
+      <c r="X9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y9" s="22" t="n">
+        <v>3612</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1583,6 +1637,12 @@
       <c r="W10" s="22" t="n">
         <v>2668</v>
       </c>
+      <c r="X10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y10" s="22" t="n">
+        <v>2677</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1660,6 +1720,12 @@
       <c r="W11" s="22" t="n">
         <v>942</v>
       </c>
+      <c r="X11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y11" s="22" t="n">
+        <v>946</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1737,6 +1803,12 @@
       <c r="W12" s="22" t="n">
         <v>1095</v>
       </c>
+      <c r="X12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y12" s="22" t="n">
+        <v>1096</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1814,6 +1886,12 @@
       <c r="W13" s="22" t="n">
         <v>2081</v>
       </c>
+      <c r="X13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y13" s="22" t="n">
+        <v>2088</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1891,6 +1969,12 @@
       <c r="W14" s="22" t="n">
         <v>2303</v>
       </c>
+      <c r="X14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y14" s="22" t="n">
+        <v>2301</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1968,6 +2052,12 @@
       <c r="W15" s="22" t="n">
         <v>2472</v>
       </c>
+      <c r="X15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y15" s="22" t="n">
+        <v>2482</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2045,6 +2135,12 @@
       <c r="W16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="X16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y16" s="22" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2122,6 +2218,12 @@
       <c r="W17" s="22" t="n">
         <v>1230</v>
       </c>
+      <c r="X17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y17" s="22" t="n">
+        <v>1234</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2199,6 +2301,12 @@
       <c r="W18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="X18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2276,6 +2384,12 @@
       <c r="W19" s="22" t="n">
         <v>858</v>
       </c>
+      <c r="X19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y19" s="22" t="n">
+        <v>859</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2353,6 +2467,12 @@
       <c r="W20" s="22" t="n">
         <v>1034</v>
       </c>
+      <c r="X20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y20" s="22" t="n">
+        <v>1035</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2430,6 +2550,12 @@
       <c r="W21" s="22" t="n">
         <v>725</v>
       </c>
+      <c r="X21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y21" s="22" t="n">
+        <v>725</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2507,6 +2633,12 @@
       <c r="W22" s="22" t="n">
         <v>590</v>
       </c>
+      <c r="X22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y22" s="22" t="n">
+        <v>594</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2584,6 +2716,12 @@
       <c r="W23" s="22" t="n">
         <v>725</v>
       </c>
+      <c r="X23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y23" s="22" t="n">
+        <v>725</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2661,6 +2799,12 @@
       <c r="W24" s="22" t="n">
         <v>1405</v>
       </c>
+      <c r="X24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y24" s="22" t="n">
+        <v>1412</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2738,6 +2882,12 @@
       <c r="W25" s="22" t="n">
         <v>573</v>
       </c>
+      <c r="X25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y25" s="22" t="n">
+        <v>577</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2815,10 +2965,17 @@
       <c r="W26" s="22" t="n">
         <v>257</v>
       </c>
+      <c r="X26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y26" s="22" t="n">
+        <v>272</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="H1:I1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -855,7 +855,13 @@
           <t>16/09/2026</t>
         </is>
       </c>
-      <c r="Y1" s="18" t="n"/>
+      <c r="Y1" s="23" t="n"/>
+      <c r="Z1" s="17" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="AA1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -979,6 +985,16 @@
         </is>
       </c>
       <c r="Y2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="Z2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AA2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1062,6 +1078,12 @@
       </c>
       <c r="X3" s="21" t="n"/>
       <c r="Y3" s="22" t="n"/>
+      <c r="Z3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA3" s="22" t="n">
+        <v>4703</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1145,6 +1167,12 @@
       <c r="Y4" s="22" t="n">
         <v>15664</v>
       </c>
+      <c r="Z4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA4" s="22" t="n">
+        <v>15671</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1228,6 +1256,12 @@
       <c r="Y5" s="22" t="n">
         <v>5150</v>
       </c>
+      <c r="Z5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA5" s="22" t="n">
+        <v>5173</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1311,6 +1345,12 @@
       <c r="Y6" s="22" t="n">
         <v>6439</v>
       </c>
+      <c r="Z6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA6" s="22" t="n">
+        <v>6438</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1394,6 +1434,12 @@
       <c r="Y7" s="22" t="n">
         <v>2202</v>
       </c>
+      <c r="Z7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA7" s="22" t="n">
+        <v>2197</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1477,6 +1523,12 @@
       <c r="Y8" s="22" t="n">
         <v>7127</v>
       </c>
+      <c r="Z8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA8" s="22" t="n">
+        <v>7134</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1560,6 +1612,12 @@
       <c r="Y9" s="22" t="n">
         <v>3612</v>
       </c>
+      <c r="Z9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA9" s="22" t="n">
+        <v>3619</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1643,6 +1701,12 @@
       <c r="Y10" s="22" t="n">
         <v>2677</v>
       </c>
+      <c r="Z10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA10" s="22" t="n">
+        <v>2675</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1726,6 +1790,12 @@
       <c r="Y11" s="22" t="n">
         <v>946</v>
       </c>
+      <c r="Z11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA11" s="22" t="n">
+        <v>957</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1809,6 +1879,12 @@
       <c r="Y12" s="22" t="n">
         <v>1096</v>
       </c>
+      <c r="Z12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA12" s="22" t="n">
+        <v>1093</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1892,6 +1968,12 @@
       <c r="Y13" s="22" t="n">
         <v>2088</v>
       </c>
+      <c r="Z13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA13" s="22" t="n">
+        <v>2122</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1975,6 +2057,12 @@
       <c r="Y14" s="22" t="n">
         <v>2301</v>
       </c>
+      <c r="Z14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA14" s="22" t="n">
+        <v>2283</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2058,6 +2146,12 @@
       <c r="Y15" s="22" t="n">
         <v>2482</v>
       </c>
+      <c r="Z15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA15" s="22" t="n">
+        <v>2477</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2141,6 +2235,12 @@
       <c r="Y16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="Z16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA16" s="22" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2224,6 +2324,12 @@
       <c r="Y17" s="22" t="n">
         <v>1234</v>
       </c>
+      <c r="Z17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA17" s="22" t="n">
+        <v>1245</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2307,6 +2413,12 @@
       <c r="Y18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="Z18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" s="22" t="n">
+        <v>418</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2390,6 +2502,12 @@
       <c r="Y19" s="22" t="n">
         <v>859</v>
       </c>
+      <c r="Z19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA19" s="22" t="n">
+        <v>862</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2473,6 +2591,12 @@
       <c r="Y20" s="22" t="n">
         <v>1035</v>
       </c>
+      <c r="Z20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA20" s="22" t="n">
+        <v>1035</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2556,6 +2680,12 @@
       <c r="Y21" s="22" t="n">
         <v>725</v>
       </c>
+      <c r="Z21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA21" s="22" t="n">
+        <v>725</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2639,6 +2769,12 @@
       <c r="Y22" s="22" t="n">
         <v>594</v>
       </c>
+      <c r="Z22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA22" s="22" t="n">
+        <v>596</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2722,6 +2858,12 @@
       <c r="Y23" s="22" t="n">
         <v>725</v>
       </c>
+      <c r="Z23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA23" s="22" t="n">
+        <v>725</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2805,6 +2947,12 @@
       <c r="Y24" s="22" t="n">
         <v>1412</v>
       </c>
+      <c r="Z24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA24" s="22" t="n">
+        <v>1414</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2888,6 +3036,12 @@
       <c r="Y25" s="22" t="n">
         <v>577</v>
       </c>
+      <c r="Z25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA25" s="22" t="n">
+        <v>578</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2971,14 +3125,21 @@
       <c r="Y26" s="22" t="n">
         <v>272</v>
       </c>
+      <c r="Z26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA26" s="22" t="n">
+        <v>273</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -861,7 +861,7 @@
           <t>17/09/2026</t>
         </is>
       </c>
-      <c r="AA1" s="18" t="n"/>
+      <c r="AA1" s="23" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1082,7 +1082,7 @@
         <v>4.4</v>
       </c>
       <c r="AA3" s="22" t="n">
-        <v>4703</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
@@ -1171,7 +1171,7 @@
         <v>4.3</v>
       </c>
       <c r="AA4" s="22" t="n">
-        <v>15671</v>
+        <v>15676</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
@@ -1260,7 +1260,7 @@
         <v>4.5</v>
       </c>
       <c r="AA5" s="22" t="n">
-        <v>5173</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
@@ -1438,7 +1438,7 @@
         <v>4.5</v>
       </c>
       <c r="AA7" s="22" t="n">
-        <v>2197</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
@@ -1616,7 +1616,7 @@
         <v>4.4</v>
       </c>
       <c r="AA9" s="22" t="n">
-        <v>3619</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
@@ -1705,7 +1705,7 @@
         <v>4.4</v>
       </c>
       <c r="AA10" s="22" t="n">
-        <v>2675</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
@@ -1794,7 +1794,7 @@
         <v>4.7</v>
       </c>
       <c r="AA11" s="22" t="n">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
@@ -1972,7 +1972,7 @@
         <v>4.7</v>
       </c>
       <c r="AA13" s="22" t="n">
-        <v>2122</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
@@ -2150,7 +2150,7 @@
         <v>4.4</v>
       </c>
       <c r="AA15" s="22" t="n">
-        <v>2477</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -2506,7 +2506,7 @@
         <v>4.7</v>
       </c>
       <c r="AA19" s="22" t="n">
-        <v>862</v>
+        <v>868</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
@@ -2595,7 +2595,7 @@
         <v>4.6</v>
       </c>
       <c r="AA20" s="22" t="n">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
@@ -2684,7 +2684,7 @@
         <v>4.6</v>
       </c>
       <c r="AA21" s="22" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
@@ -2773,7 +2773,7 @@
         <v>4.7</v>
       </c>
       <c r="AA22" s="22" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
@@ -2862,7 +2862,7 @@
         <v>4.6</v>
       </c>
       <c r="AA23" s="22" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
@@ -3040,7 +3040,7 @@
         <v>4.7</v>
       </c>
       <c r="AA25" s="22" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
@@ -3138,8 +3138,8 @@
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="T1:U1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -862,6 +862,12 @@
         </is>
       </c>
       <c r="AA1" s="23" t="n"/>
+      <c r="AB1" s="17" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="AC1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -995,6 +1001,16 @@
         </is>
       </c>
       <c r="AA2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AB2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AC2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1084,6 +1100,12 @@
       <c r="AA3" s="22" t="n">
         <v>4706</v>
       </c>
+      <c r="AB3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC3" s="22" t="n">
+        <v>4709</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1173,6 +1195,12 @@
       <c r="AA4" s="22" t="n">
         <v>15676</v>
       </c>
+      <c r="AB4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC4" s="22" t="n">
+        <v>15681</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1262,6 +1290,12 @@
       <c r="AA5" s="22" t="n">
         <v>5185</v>
       </c>
+      <c r="AB5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC5" s="22" t="n">
+        <v>5185</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1351,6 +1385,12 @@
       <c r="AA6" s="22" t="n">
         <v>6438</v>
       </c>
+      <c r="AB6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC6" s="22" t="n">
+        <v>6433</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1440,6 +1480,12 @@
       <c r="AA7" s="22" t="n">
         <v>2198</v>
       </c>
+      <c r="AB7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC7" s="22" t="n">
+        <v>2201</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1529,6 +1575,12 @@
       <c r="AA8" s="22" t="n">
         <v>7134</v>
       </c>
+      <c r="AB8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC8" s="22" t="n">
+        <v>7136</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1618,6 +1670,12 @@
       <c r="AA9" s="22" t="n">
         <v>3624</v>
       </c>
+      <c r="AB9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC9" s="22" t="n">
+        <v>3634</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1707,6 +1765,12 @@
       <c r="AA10" s="22" t="n">
         <v>2677</v>
       </c>
+      <c r="AB10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC10" s="22" t="n">
+        <v>2673</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1796,6 +1860,12 @@
       <c r="AA11" s="22" t="n">
         <v>960</v>
       </c>
+      <c r="AB11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC11" s="22" t="n">
+        <v>963</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1885,6 +1955,12 @@
       <c r="AA12" s="22" t="n">
         <v>1093</v>
       </c>
+      <c r="AB12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC12" s="22" t="n">
+        <v>1093</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1974,6 +2050,12 @@
       <c r="AA13" s="22" t="n">
         <v>2128</v>
       </c>
+      <c r="AB13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC13" s="22" t="n">
+        <v>2142</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2063,6 +2145,12 @@
       <c r="AA14" s="22" t="n">
         <v>2283</v>
       </c>
+      <c r="AB14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC14" s="22" t="n">
+        <v>2277</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2152,6 +2240,12 @@
       <c r="AA15" s="22" t="n">
         <v>2478</v>
       </c>
+      <c r="AB15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC15" s="22" t="n">
+        <v>2476</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2241,6 +2335,12 @@
       <c r="AA16" s="22" t="n">
         <v>787</v>
       </c>
+      <c r="AB16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC16" s="22" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2330,6 +2430,12 @@
       <c r="AA17" s="22" t="n">
         <v>1245</v>
       </c>
+      <c r="AB17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC17" s="22" t="n">
+        <v>1250</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2419,6 +2525,12 @@
       <c r="AA18" s="22" t="n">
         <v>418</v>
       </c>
+      <c r="AB18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC18" s="22" t="n">
+        <v>419</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2508,6 +2620,12 @@
       <c r="AA19" s="22" t="n">
         <v>868</v>
       </c>
+      <c r="AB19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC19" s="22" t="n">
+        <v>875</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2597,6 +2715,12 @@
       <c r="AA20" s="22" t="n">
         <v>1036</v>
       </c>
+      <c r="AB20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC20" s="22" t="n">
+        <v>1037</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2686,6 +2810,12 @@
       <c r="AA21" s="22" t="n">
         <v>726</v>
       </c>
+      <c r="AB21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC21" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2775,6 +2905,12 @@
       <c r="AA22" s="22" t="n">
         <v>597</v>
       </c>
+      <c r="AB22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC22" s="22" t="n">
+        <v>595</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2864,6 +3000,12 @@
       <c r="AA23" s="22" t="n">
         <v>726</v>
       </c>
+      <c r="AB23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC23" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2953,6 +3095,12 @@
       <c r="AA24" s="22" t="n">
         <v>1414</v>
       </c>
+      <c r="AB24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC24" s="22" t="n">
+        <v>1414</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3042,6 +3190,12 @@
       <c r="AA25" s="22" t="n">
         <v>579</v>
       </c>
+      <c r="AB25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC25" s="22" t="n">
+        <v>579</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -3131,15 +3285,22 @@
       <c r="AA26" s="22" t="n">
         <v>273</v>
       </c>
+      <c r="AB26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC26" s="22" t="n">
+        <v>275</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="T1:U1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="H1:I1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -867,7 +867,13 @@
           <t>18/09/2026</t>
         </is>
       </c>
-      <c r="AC1" s="18" t="n"/>
+      <c r="AC1" s="23" t="n"/>
+      <c r="AD1" s="17" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="AE1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1011,6 +1017,16 @@
         </is>
       </c>
       <c r="AC2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AD2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AE2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1106,6 +1122,12 @@
       <c r="AC3" s="22" t="n">
         <v>4709</v>
       </c>
+      <c r="AD3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE3" s="22" t="n">
+        <v>4711</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1201,6 +1223,12 @@
       <c r="AC4" s="22" t="n">
         <v>15681</v>
       </c>
+      <c r="AD4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE4" s="22" t="n">
+        <v>15693</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1296,6 +1324,12 @@
       <c r="AC5" s="22" t="n">
         <v>5185</v>
       </c>
+      <c r="AD5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE5" s="22" t="n">
+        <v>5184</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1391,6 +1425,12 @@
       <c r="AC6" s="22" t="n">
         <v>6433</v>
       </c>
+      <c r="AD6" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE6" s="22" t="n">
+        <v>4711</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1486,6 +1526,12 @@
       <c r="AC7" s="22" t="n">
         <v>2201</v>
       </c>
+      <c r="AD7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE7" s="22" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1581,6 +1627,12 @@
       <c r="AC8" s="22" t="n">
         <v>7136</v>
       </c>
+      <c r="AD8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE8" s="22" t="n">
+        <v>7133</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1676,6 +1728,12 @@
       <c r="AC9" s="22" t="n">
         <v>3634</v>
       </c>
+      <c r="AD9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE9" s="22" t="n">
+        <v>3632</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1771,6 +1829,12 @@
       <c r="AC10" s="22" t="n">
         <v>2673</v>
       </c>
+      <c r="AD10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE10" s="22" t="n">
+        <v>2671</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1866,6 +1930,12 @@
       <c r="AC11" s="22" t="n">
         <v>963</v>
       </c>
+      <c r="AD11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE11" s="22" t="n">
+        <v>972</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1961,6 +2031,12 @@
       <c r="AC12" s="22" t="n">
         <v>1093</v>
       </c>
+      <c r="AD12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE12" s="22" t="n">
+        <v>1093</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2056,6 +2132,12 @@
       <c r="AC13" s="22" t="n">
         <v>2142</v>
       </c>
+      <c r="AD13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE13" s="22" t="n">
+        <v>2151</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2151,6 +2233,12 @@
       <c r="AC14" s="22" t="n">
         <v>2277</v>
       </c>
+      <c r="AD14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE14" s="22" t="n">
+        <v>2267</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2246,6 +2334,12 @@
       <c r="AC15" s="22" t="n">
         <v>2476</v>
       </c>
+      <c r="AD15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE15" s="22" t="n">
+        <v>2480</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2341,6 +2435,12 @@
       <c r="AC16" s="22" t="n">
         <v>787</v>
       </c>
+      <c r="AD16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE16" s="22" t="n">
+        <v>792</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2436,6 +2536,12 @@
       <c r="AC17" s="22" t="n">
         <v>1250</v>
       </c>
+      <c r="AD17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE17" s="22" t="n">
+        <v>1253</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2531,6 +2637,12 @@
       <c r="AC18" s="22" t="n">
         <v>419</v>
       </c>
+      <c r="AD18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE18" s="22" t="n">
+        <v>421</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2626,6 +2738,12 @@
       <c r="AC19" s="22" t="n">
         <v>875</v>
       </c>
+      <c r="AD19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE19" s="22" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2721,6 +2839,12 @@
       <c r="AC20" s="22" t="n">
         <v>1037</v>
       </c>
+      <c r="AD20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE20" s="22" t="n">
+        <v>1039</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2816,6 +2940,12 @@
       <c r="AC21" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AD21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE21" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -2911,6 +3041,12 @@
       <c r="AC22" s="22" t="n">
         <v>595</v>
       </c>
+      <c r="AD22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE22" s="22" t="n">
+        <v>596</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3006,6 +3142,12 @@
       <c r="AC23" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AD23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE23" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3101,6 +3243,12 @@
       <c r="AC24" s="22" t="n">
         <v>1414</v>
       </c>
+      <c r="AD24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE24" s="22" t="n">
+        <v>1410</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3196,6 +3344,12 @@
       <c r="AC25" s="22" t="n">
         <v>579</v>
       </c>
+      <c r="AD25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE25" s="22" t="n">
+        <v>576</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -3291,11 +3445,18 @@
       <c r="AC26" s="22" t="n">
         <v>275</v>
       </c>
+      <c r="AD26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE26" s="22" t="n">
+        <v>273</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="T1:U1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE26"/>
+  <dimension ref="A1:AG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -873,7 +873,13 @@
           <t>19/09/2026</t>
         </is>
       </c>
-      <c r="AE1" s="18" t="n"/>
+      <c r="AE1" s="23" t="n"/>
+      <c r="AF1" s="17" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="AG1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1027,6 +1033,16 @@
         </is>
       </c>
       <c r="AE2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AF2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AG2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1128,6 +1144,12 @@
       <c r="AE3" s="22" t="n">
         <v>4711</v>
       </c>
+      <c r="AF3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG3" s="22" t="n">
+        <v>4713</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1229,6 +1251,12 @@
       <c r="AE4" s="22" t="n">
         <v>15693</v>
       </c>
+      <c r="AF4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG4" s="22" t="n">
+        <v>15696</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1330,6 +1358,12 @@
       <c r="AE5" s="22" t="n">
         <v>5184</v>
       </c>
+      <c r="AF5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG5" s="22" t="n">
+        <v>5198</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1431,6 +1465,12 @@
       <c r="AE6" s="22" t="n">
         <v>4711</v>
       </c>
+      <c r="AF6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG6" s="22" t="n">
+        <v>6435</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1532,6 +1572,12 @@
       <c r="AE7" s="22" t="n">
         <v>2216</v>
       </c>
+      <c r="AF7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG7" s="22" t="n">
+        <v>2228</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1633,6 +1679,12 @@
       <c r="AE8" s="22" t="n">
         <v>7133</v>
       </c>
+      <c r="AF8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG8" s="22" t="n">
+        <v>7152</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1734,6 +1786,12 @@
       <c r="AE9" s="22" t="n">
         <v>3632</v>
       </c>
+      <c r="AF9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG9" s="22" t="n">
+        <v>3668</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1835,6 +1893,12 @@
       <c r="AE10" s="22" t="n">
         <v>2671</v>
       </c>
+      <c r="AF10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG10" s="22" t="n">
+        <v>2672</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1936,6 +2000,12 @@
       <c r="AE11" s="22" t="n">
         <v>972</v>
       </c>
+      <c r="AF11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG11" s="22" t="n">
+        <v>973</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2037,6 +2107,12 @@
       <c r="AE12" s="22" t="n">
         <v>1093</v>
       </c>
+      <c r="AF12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG12" s="22" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2138,6 +2214,12 @@
       <c r="AE13" s="22" t="n">
         <v>2151</v>
       </c>
+      <c r="AF13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG13" s="22" t="n">
+        <v>2206</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2239,6 +2321,12 @@
       <c r="AE14" s="22" t="n">
         <v>2267</v>
       </c>
+      <c r="AF14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG14" s="22" t="n">
+        <v>2263</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2340,6 +2428,12 @@
       <c r="AE15" s="22" t="n">
         <v>2480</v>
       </c>
+      <c r="AF15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG15" s="22" t="n">
+        <v>2489</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2441,6 +2535,12 @@
       <c r="AE16" s="22" t="n">
         <v>792</v>
       </c>
+      <c r="AF16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG16" s="22" t="n">
+        <v>803</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2542,6 +2642,12 @@
       <c r="AE17" s="22" t="n">
         <v>1253</v>
       </c>
+      <c r="AF17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG17" s="22" t="n">
+        <v>1259</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2643,6 +2749,12 @@
       <c r="AE18" s="22" t="n">
         <v>421</v>
       </c>
+      <c r="AF18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG18" s="22" t="n">
+        <v>421</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2744,6 +2856,12 @@
       <c r="AE19" s="22" t="n">
         <v>885</v>
       </c>
+      <c r="AF19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG19" s="22" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2845,6 +2963,12 @@
       <c r="AE20" s="22" t="n">
         <v>1039</v>
       </c>
+      <c r="AF20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG20" s="22" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -2946,6 +3070,12 @@
       <c r="AE21" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AF21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG21" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3047,6 +3177,12 @@
       <c r="AE22" s="22" t="n">
         <v>596</v>
       </c>
+      <c r="AF22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG22" s="22" t="n">
+        <v>597</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3148,6 +3284,12 @@
       <c r="AE23" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AF23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG23" s="22" t="n">
+        <v>616</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3249,6 +3391,12 @@
       <c r="AE24" s="22" t="n">
         <v>1410</v>
       </c>
+      <c r="AF24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG24" s="22" t="n">
+        <v>1415</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3350,6 +3498,12 @@
       <c r="AE25" s="22" t="n">
         <v>576</v>
       </c>
+      <c r="AF25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG25" s="22" t="n">
+        <v>579</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -3451,11 +3605,18 @@
       <c r="AE26" s="22" t="n">
         <v>273</v>
       </c>
+      <c r="AF26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG26" s="22" t="n">
+        <v>278</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="V1:W1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG26"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -879,7 +879,13 @@
           <t>20/09/2026</t>
         </is>
       </c>
-      <c r="AG1" s="18" t="n"/>
+      <c r="AG1" s="23" t="n"/>
+      <c r="AH1" s="17" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="AI1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1043,6 +1049,16 @@
         </is>
       </c>
       <c r="AG2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AH2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AI2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1150,6 +1166,12 @@
       <c r="AG3" s="22" t="n">
         <v>4713</v>
       </c>
+      <c r="AH3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI3" s="22" t="n">
+        <v>4715</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1257,6 +1279,12 @@
       <c r="AG4" s="22" t="n">
         <v>15696</v>
       </c>
+      <c r="AH4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AI4" s="22" t="n">
+        <v>15687</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1364,6 +1392,12 @@
       <c r="AG5" s="22" t="n">
         <v>5198</v>
       </c>
+      <c r="AH5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI5" s="22" t="n">
+        <v>5205</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1471,6 +1505,12 @@
       <c r="AG6" s="22" t="n">
         <v>6435</v>
       </c>
+      <c r="AH6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AI6" s="22" t="n">
+        <v>6438</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1578,6 +1618,12 @@
       <c r="AG7" s="22" t="n">
         <v>2228</v>
       </c>
+      <c r="AH7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI7" s="22" t="n">
+        <v>2229</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1685,6 +1731,12 @@
       <c r="AG8" s="22" t="n">
         <v>7152</v>
       </c>
+      <c r="AH8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI8" s="22" t="n">
+        <v>7162</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1792,6 +1844,12 @@
       <c r="AG9" s="22" t="n">
         <v>3668</v>
       </c>
+      <c r="AH9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI9" s="22" t="n">
+        <v>3663</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1899,6 +1957,12 @@
       <c r="AG10" s="22" t="n">
         <v>2672</v>
       </c>
+      <c r="AH10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI10" s="22" t="n">
+        <v>2674</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2006,6 +2070,12 @@
       <c r="AG11" s="22" t="n">
         <v>973</v>
       </c>
+      <c r="AH11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI11" s="22" t="n">
+        <v>978</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2113,6 +2183,12 @@
       <c r="AG12" s="22" t="n">
         <v>1094</v>
       </c>
+      <c r="AH12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI12" s="22" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2220,6 +2296,12 @@
       <c r="AG13" s="22" t="n">
         <v>2206</v>
       </c>
+      <c r="AH13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI13" s="22" t="n">
+        <v>2194</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2327,6 +2409,12 @@
       <c r="AG14" s="22" t="n">
         <v>2263</v>
       </c>
+      <c r="AH14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI14" s="22" t="n">
+        <v>2257</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2434,6 +2522,12 @@
       <c r="AG15" s="22" t="n">
         <v>2489</v>
       </c>
+      <c r="AH15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI15" s="22" t="n">
+        <v>2487</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2541,6 +2635,12 @@
       <c r="AG16" s="22" t="n">
         <v>803</v>
       </c>
+      <c r="AH16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI16" s="22" t="n">
+        <v>811</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2648,6 +2748,12 @@
       <c r="AG17" s="22" t="n">
         <v>1259</v>
       </c>
+      <c r="AH17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI17" s="22" t="n">
+        <v>1260</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2755,6 +2861,12 @@
       <c r="AG18" s="22" t="n">
         <v>421</v>
       </c>
+      <c r="AH18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AI18" s="22" t="n">
+        <v>423</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2862,6 +2974,12 @@
       <c r="AG19" s="22" t="n">
         <v>895</v>
       </c>
+      <c r="AH19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI19" s="22" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -2969,6 +3087,12 @@
       <c r="AG20" s="22" t="n">
         <v>1042</v>
       </c>
+      <c r="AH20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AI20" s="22" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3076,6 +3200,12 @@
       <c r="AG21" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AH21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AI21" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3183,6 +3313,12 @@
       <c r="AG22" s="22" t="n">
         <v>597</v>
       </c>
+      <c r="AH22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI22" s="22" t="n">
+        <v>602</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3290,6 +3426,12 @@
       <c r="AG23" s="22" t="n">
         <v>616</v>
       </c>
+      <c r="AH23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AI23" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3397,6 +3539,12 @@
       <c r="AG24" s="22" t="n">
         <v>1415</v>
       </c>
+      <c r="AH24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AI24" s="22" t="n">
+        <v>1418</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3504,6 +3652,12 @@
       <c r="AG25" s="22" t="n">
         <v>579</v>
       </c>
+      <c r="AH25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AI25" s="22" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -3611,9 +3765,15 @@
       <c r="AG26" s="22" t="n">
         <v>278</v>
       </c>
+      <c r="AH26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AI26" s="22" t="n">
+        <v>280</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -3627,6 +3787,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
   </mergeCells>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -885,7 +885,13 @@
           <t>21/09/2026</t>
         </is>
       </c>
-      <c r="AI1" s="18" t="n"/>
+      <c r="AI1" s="23" t="n"/>
+      <c r="AJ1" s="17" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="AK1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1059,6 +1065,16 @@
         </is>
       </c>
       <c r="AI2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AJ2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AK2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1172,6 +1188,12 @@
       <c r="AI3" s="22" t="n">
         <v>4715</v>
       </c>
+      <c r="AJ3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK3" s="22" t="n">
+        <v>4727</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1285,6 +1307,12 @@
       <c r="AI4" s="22" t="n">
         <v>15687</v>
       </c>
+      <c r="AJ4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK4" s="22" t="n">
+        <v>15688</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1398,6 +1426,12 @@
       <c r="AI5" s="22" t="n">
         <v>5205</v>
       </c>
+      <c r="AJ5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK5" s="22" t="n">
+        <v>5210</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1511,6 +1545,12 @@
       <c r="AI6" s="22" t="n">
         <v>6438</v>
       </c>
+      <c r="AJ6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK6" s="22" t="n">
+        <v>6444</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1624,6 +1664,12 @@
       <c r="AI7" s="22" t="n">
         <v>2229</v>
       </c>
+      <c r="AJ7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK7" s="22" t="n">
+        <v>2230</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1737,6 +1783,12 @@
       <c r="AI8" s="22" t="n">
         <v>7162</v>
       </c>
+      <c r="AJ8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK8" s="22" t="n">
+        <v>7175</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1850,6 +1902,12 @@
       <c r="AI9" s="22" t="n">
         <v>3663</v>
       </c>
+      <c r="AJ9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK9" s="22" t="n">
+        <v>3670</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1963,6 +2021,12 @@
       <c r="AI10" s="22" t="n">
         <v>2674</v>
       </c>
+      <c r="AJ10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK10" s="22" t="n">
+        <v>2675</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2076,6 +2140,12 @@
       <c r="AI11" s="22" t="n">
         <v>978</v>
       </c>
+      <c r="AJ11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK11" s="22" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2189,6 +2259,12 @@
       <c r="AI12" s="22" t="n">
         <v>1094</v>
       </c>
+      <c r="AJ12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK12" s="22" t="n">
+        <v>1095</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2302,6 +2378,12 @@
       <c r="AI13" s="22" t="n">
         <v>2194</v>
       </c>
+      <c r="AJ13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK13" s="22" t="n">
+        <v>2192</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2415,6 +2497,12 @@
       <c r="AI14" s="22" t="n">
         <v>2257</v>
       </c>
+      <c r="AJ14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK14" s="22" t="n">
+        <v>2267</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2528,6 +2616,12 @@
       <c r="AI15" s="22" t="n">
         <v>2487</v>
       </c>
+      <c r="AJ15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK15" s="22" t="n">
+        <v>2492</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2641,6 +2735,12 @@
       <c r="AI16" s="22" t="n">
         <v>811</v>
       </c>
+      <c r="AJ16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK16" s="22" t="n">
+        <v>823</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2754,6 +2854,12 @@
       <c r="AI17" s="22" t="n">
         <v>1260</v>
       </c>
+      <c r="AJ17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK17" s="22" t="n">
+        <v>1262</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2867,6 +2973,12 @@
       <c r="AI18" s="22" t="n">
         <v>423</v>
       </c>
+      <c r="AJ18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AK18" s="22" t="n">
+        <v>423</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -2980,6 +3092,12 @@
       <c r="AI19" s="22" t="n">
         <v>896</v>
       </c>
+      <c r="AJ19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK19" s="22" t="n">
+        <v>890</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3093,6 +3211,12 @@
       <c r="AI20" s="22" t="n">
         <v>1043</v>
       </c>
+      <c r="AJ20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK20" s="22" t="n">
+        <v>1044</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3206,6 +3330,12 @@
       <c r="AI21" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AJ21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK21" s="22" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3319,6 +3449,12 @@
       <c r="AI22" s="22" t="n">
         <v>602</v>
       </c>
+      <c r="AJ22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK22" s="22" t="n">
+        <v>604</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3432,6 +3568,12 @@
       <c r="AI23" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AJ23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK23" s="22" t="n">
+        <v>618</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3545,6 +3687,12 @@
       <c r="AI24" s="22" t="n">
         <v>1418</v>
       </c>
+      <c r="AJ24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK24" s="22" t="n">
+        <v>1418</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3658,6 +3806,12 @@
       <c r="AI25" s="22" t="n">
         <v>585</v>
       </c>
+      <c r="AJ25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK25" s="22" t="n">
+        <v>587</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -3771,9 +3925,15 @@
       <c r="AI26" s="22" t="n">
         <v>280</v>
       </c>
+      <c r="AJ26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK26" s="22" t="n">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -3788,6 +3948,7 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
   </mergeCells>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -891,7 +891,13 @@
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="AK1" s="18" t="n"/>
+      <c r="AK1" s="23" t="n"/>
+      <c r="AL1" s="17" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="AM1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1075,6 +1081,16 @@
         </is>
       </c>
       <c r="AK2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AL2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AM2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1194,6 +1210,12 @@
       <c r="AK3" s="22" t="n">
         <v>4727</v>
       </c>
+      <c r="AL3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM3" s="22" t="n">
+        <v>4731</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1313,6 +1335,12 @@
       <c r="AK4" s="22" t="n">
         <v>15688</v>
       </c>
+      <c r="AL4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AM4" s="22" t="n">
+        <v>15693</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1432,6 +1460,12 @@
       <c r="AK5" s="22" t="n">
         <v>5210</v>
       </c>
+      <c r="AL5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM5" s="22" t="n">
+        <v>5219</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1551,6 +1585,12 @@
       <c r="AK6" s="22" t="n">
         <v>6444</v>
       </c>
+      <c r="AL6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AM6" s="22" t="n">
+        <v>6438</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1670,6 +1710,12 @@
       <c r="AK7" s="22" t="n">
         <v>2230</v>
       </c>
+      <c r="AL7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM7" s="22" t="n">
+        <v>2236</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1789,6 +1835,12 @@
       <c r="AK8" s="22" t="n">
         <v>7175</v>
       </c>
+      <c r="AL8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM8" s="22" t="n">
+        <v>7182</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1908,6 +1960,12 @@
       <c r="AK9" s="22" t="n">
         <v>3670</v>
       </c>
+      <c r="AL9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM9" s="22" t="n">
+        <v>3655</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2027,6 +2085,12 @@
       <c r="AK10" s="22" t="n">
         <v>2675</v>
       </c>
+      <c r="AL10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM10" s="22" t="n">
+        <v>2679</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2146,6 +2210,12 @@
       <c r="AK11" s="22" t="n">
         <v>983</v>
       </c>
+      <c r="AL11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM11" s="22" t="n">
+        <v>999</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2265,6 +2335,12 @@
       <c r="AK12" s="22" t="n">
         <v>1095</v>
       </c>
+      <c r="AL12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM12" s="22" t="n">
+        <v>1095</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2384,6 +2460,12 @@
       <c r="AK13" s="22" t="n">
         <v>2192</v>
       </c>
+      <c r="AL13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM13" s="22" t="n">
+        <v>2180</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2503,6 +2585,12 @@
       <c r="AK14" s="22" t="n">
         <v>2267</v>
       </c>
+      <c r="AL14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM14" s="22" t="n">
+        <v>2272</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2622,6 +2710,12 @@
       <c r="AK15" s="22" t="n">
         <v>2492</v>
       </c>
+      <c r="AL15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM15" s="22" t="n">
+        <v>2505</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2741,6 +2835,12 @@
       <c r="AK16" s="22" t="n">
         <v>823</v>
       </c>
+      <c r="AL16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM16" s="22" t="n">
+        <v>823</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2860,6 +2960,12 @@
       <c r="AK17" s="22" t="n">
         <v>1262</v>
       </c>
+      <c r="AL17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM17" s="22" t="n">
+        <v>1265</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -2979,6 +3085,12 @@
       <c r="AK18" s="22" t="n">
         <v>423</v>
       </c>
+      <c r="AL18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AM18" s="22" t="n">
+        <v>423</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3098,6 +3210,12 @@
       <c r="AK19" s="22" t="n">
         <v>890</v>
       </c>
+      <c r="AL19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM19" s="22" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3217,6 +3335,12 @@
       <c r="AK20" s="22" t="n">
         <v>1044</v>
       </c>
+      <c r="AL20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AM20" s="22" t="n">
+        <v>1045</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3336,6 +3460,12 @@
       <c r="AK21" s="22" t="n">
         <v>728</v>
       </c>
+      <c r="AL21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AM21" s="22" t="n">
+        <v>730</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3455,6 +3585,12 @@
       <c r="AK22" s="22" t="n">
         <v>604</v>
       </c>
+      <c r="AL22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM22" s="22" t="n">
+        <v>606</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3574,6 +3710,12 @@
       <c r="AK23" s="22" t="n">
         <v>618</v>
       </c>
+      <c r="AL23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM23" s="22" t="n">
+        <v>628</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3693,6 +3835,12 @@
       <c r="AK24" s="22" t="n">
         <v>1418</v>
       </c>
+      <c r="AL24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AM24" s="22" t="n">
+        <v>1419</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3812,6 +3960,12 @@
       <c r="AK25" s="22" t="n">
         <v>587</v>
       </c>
+      <c r="AL25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AM25" s="22" t="n">
+        <v>588</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -3931,9 +4085,15 @@
       <c r="AK26" s="22" t="n">
         <v>282</v>
       </c>
+      <c r="AL26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AM26" s="22" t="n">
+        <v>283</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -3949,6 +4109,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
   </mergeCells>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AO26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -897,7 +897,13 @@
           <t>23/09/2026</t>
         </is>
       </c>
-      <c r="AM1" s="18" t="n"/>
+      <c r="AM1" s="23" t="n"/>
+      <c r="AN1" s="17" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="AO1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1091,6 +1097,16 @@
         </is>
       </c>
       <c r="AM2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AN2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AO2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1216,6 +1232,12 @@
       <c r="AM3" s="22" t="n">
         <v>4731</v>
       </c>
+      <c r="AN3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO3" s="22" t="n">
+        <v>4737</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1341,6 +1363,12 @@
       <c r="AM4" s="22" t="n">
         <v>15693</v>
       </c>
+      <c r="AN4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO4" s="22" t="n">
+        <v>15699</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1466,6 +1494,12 @@
       <c r="AM5" s="22" t="n">
         <v>5219</v>
       </c>
+      <c r="AN5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO5" s="22" t="n">
+        <v>5241</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1591,6 +1625,12 @@
       <c r="AM6" s="22" t="n">
         <v>6438</v>
       </c>
+      <c r="AN6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO6" s="22" t="n">
+        <v>6438</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1716,6 +1756,12 @@
       <c r="AM7" s="22" t="n">
         <v>2236</v>
       </c>
+      <c r="AN7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO7" s="22" t="n">
+        <v>2249</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1841,6 +1887,12 @@
       <c r="AM8" s="22" t="n">
         <v>7182</v>
       </c>
+      <c r="AN8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO8" s="22" t="n">
+        <v>7204</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1966,6 +2018,12 @@
       <c r="AM9" s="22" t="n">
         <v>3655</v>
       </c>
+      <c r="AN9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO9" s="22" t="n">
+        <v>3656</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2091,6 +2149,12 @@
       <c r="AM10" s="22" t="n">
         <v>2679</v>
       </c>
+      <c r="AN10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO10" s="22" t="n">
+        <v>2684</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2216,6 +2280,12 @@
       <c r="AM11" s="22" t="n">
         <v>999</v>
       </c>
+      <c r="AN11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO11" s="22" t="n">
+        <v>1005</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2341,6 +2411,12 @@
       <c r="AM12" s="22" t="n">
         <v>1095</v>
       </c>
+      <c r="AN12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO12" s="22" t="n">
+        <v>1095</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2466,6 +2542,12 @@
       <c r="AM13" s="22" t="n">
         <v>2180</v>
       </c>
+      <c r="AN13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO13" s="22" t="n">
+        <v>2169</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2591,6 +2673,12 @@
       <c r="AM14" s="22" t="n">
         <v>2272</v>
       </c>
+      <c r="AN14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO14" s="22" t="n">
+        <v>2292</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2716,6 +2804,12 @@
       <c r="AM15" s="22" t="n">
         <v>2505</v>
       </c>
+      <c r="AN15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO15" s="22" t="n">
+        <v>2523</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2841,6 +2935,12 @@
       <c r="AM16" s="22" t="n">
         <v>823</v>
       </c>
+      <c r="AN16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO16" s="22" t="n">
+        <v>827</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -2966,6 +3066,12 @@
       <c r="AM17" s="22" t="n">
         <v>1265</v>
       </c>
+      <c r="AN17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO17" s="22" t="n">
+        <v>1271</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3091,6 +3197,12 @@
       <c r="AM18" s="22" t="n">
         <v>423</v>
       </c>
+      <c r="AN18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO18" s="22" t="n">
+        <v>425</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3216,6 +3328,12 @@
       <c r="AM19" s="22" t="n">
         <v>900</v>
       </c>
+      <c r="AN19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO19" s="22" t="n">
+        <v>902</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3341,6 +3459,12 @@
       <c r="AM20" s="22" t="n">
         <v>1045</v>
       </c>
+      <c r="AN20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO20" s="22" t="n">
+        <v>1045</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3466,6 +3590,12 @@
       <c r="AM21" s="22" t="n">
         <v>730</v>
       </c>
+      <c r="AN21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO21" s="22" t="n">
+        <v>730</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3591,6 +3721,12 @@
       <c r="AM22" s="22" t="n">
         <v>606</v>
       </c>
+      <c r="AN22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO22" s="22" t="n">
+        <v>614</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3716,6 +3852,12 @@
       <c r="AM23" s="22" t="n">
         <v>628</v>
       </c>
+      <c r="AN23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO23" s="22" t="n">
+        <v>640</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3841,6 +3983,12 @@
       <c r="AM24" s="22" t="n">
         <v>1419</v>
       </c>
+      <c r="AN24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO24" s="22" t="n">
+        <v>1417</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -3966,6 +4114,12 @@
       <c r="AM25" s="22" t="n">
         <v>588</v>
       </c>
+      <c r="AN25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO25" s="22" t="n">
+        <v>595</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -4091,24 +4245,31 @@
       <c r="AM26" s="22" t="n">
         <v>283</v>
       </c>
+      <c r="AN26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO26" s="22" t="n">
+        <v>287</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
+  <mergeCells count="19">
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO26"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -903,7 +903,13 @@
           <t>24/09/2026</t>
         </is>
       </c>
-      <c r="AO1" s="18" t="n"/>
+      <c r="AO1" s="23" t="n"/>
+      <c r="AP1" s="17" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="AQ1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1107,6 +1113,16 @@
         </is>
       </c>
       <c r="AO2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AP2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AQ2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1238,6 +1254,12 @@
       <c r="AO3" s="22" t="n">
         <v>4737</v>
       </c>
+      <c r="AP3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ3" s="22" t="n">
+        <v>4744</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1369,6 +1391,12 @@
       <c r="AO4" s="22" t="n">
         <v>15699</v>
       </c>
+      <c r="AP4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ4" s="22" t="n">
+        <v>15707</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1500,6 +1528,12 @@
       <c r="AO5" s="22" t="n">
         <v>5241</v>
       </c>
+      <c r="AP5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ5" s="22" t="n">
+        <v>5264</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1631,6 +1665,12 @@
       <c r="AO6" s="22" t="n">
         <v>6438</v>
       </c>
+      <c r="AP6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ6" s="22" t="n">
+        <v>6448</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1762,6 +1802,12 @@
       <c r="AO7" s="22" t="n">
         <v>2249</v>
       </c>
+      <c r="AP7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ7" s="22" t="n">
+        <v>2272</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1893,6 +1939,12 @@
       <c r="AO8" s="22" t="n">
         <v>7204</v>
       </c>
+      <c r="AP8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ8" s="22" t="n">
+        <v>7201</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2024,6 +2076,12 @@
       <c r="AO9" s="22" t="n">
         <v>3656</v>
       </c>
+      <c r="AP9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ9" s="22" t="n">
+        <v>3679</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2155,6 +2213,12 @@
       <c r="AO10" s="22" t="n">
         <v>2684</v>
       </c>
+      <c r="AP10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ10" s="22" t="n">
+        <v>2702</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2286,6 +2350,12 @@
       <c r="AO11" s="22" t="n">
         <v>1005</v>
       </c>
+      <c r="AP11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ11" s="22" t="n">
+        <v>1032</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2417,6 +2487,12 @@
       <c r="AO12" s="22" t="n">
         <v>1095</v>
       </c>
+      <c r="AP12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ12" s="22" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2548,6 +2624,12 @@
       <c r="AO13" s="22" t="n">
         <v>2169</v>
       </c>
+      <c r="AP13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ13" s="22" t="n">
+        <v>2178</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2679,6 +2761,12 @@
       <c r="AO14" s="22" t="n">
         <v>2292</v>
       </c>
+      <c r="AP14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ14" s="22" t="n">
+        <v>2301</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2810,6 +2898,12 @@
       <c r="AO15" s="22" t="n">
         <v>2523</v>
       </c>
+      <c r="AP15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ15" s="22" t="n">
+        <v>2542</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -2941,6 +3035,12 @@
       <c r="AO16" s="22" t="n">
         <v>827</v>
       </c>
+      <c r="AP16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ16" s="22" t="n">
+        <v>834</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3072,6 +3172,12 @@
       <c r="AO17" s="22" t="n">
         <v>1271</v>
       </c>
+      <c r="AP17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ17" s="22" t="n">
+        <v>1281</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3203,6 +3309,12 @@
       <c r="AO18" s="22" t="n">
         <v>425</v>
       </c>
+      <c r="AP18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ18" s="22" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3334,6 +3446,12 @@
       <c r="AO19" s="22" t="n">
         <v>902</v>
       </c>
+      <c r="AP19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ19" s="22" t="n">
+        <v>905</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3465,6 +3583,12 @@
       <c r="AO20" s="22" t="n">
         <v>1045</v>
       </c>
+      <c r="AP20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ20" s="22" t="n">
+        <v>1056</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3596,6 +3720,12 @@
       <c r="AO21" s="22" t="n">
         <v>730</v>
       </c>
+      <c r="AP21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ21" s="22" t="n">
+        <v>729</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3727,6 +3857,12 @@
       <c r="AO22" s="22" t="n">
         <v>614</v>
       </c>
+      <c r="AP22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ22" s="22" t="n">
+        <v>620</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -3858,6 +3994,12 @@
       <c r="AO23" s="22" t="n">
         <v>640</v>
       </c>
+      <c r="AP23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ23" s="22" t="n">
+        <v>647</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -3989,6 +4131,12 @@
       <c r="AO24" s="22" t="n">
         <v>1417</v>
       </c>
+      <c r="AP24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ24" s="22" t="n">
+        <v>1418</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -4120,6 +4268,12 @@
       <c r="AO25" s="22" t="n">
         <v>595</v>
       </c>
+      <c r="AP25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ25" s="22" t="n">
+        <v>605</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -4251,9 +4405,15 @@
       <c r="AO26" s="22" t="n">
         <v>287</v>
       </c>
+      <c r="AP26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ26" s="22" t="n">
+        <v>302</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
@@ -4263,6 +4423,7 @@
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="L1:M1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -909,7 +909,13 @@
           <t>25/09/2026</t>
         </is>
       </c>
-      <c r="AQ1" s="18" t="n"/>
+      <c r="AQ1" s="23" t="n"/>
+      <c r="AR1" s="17" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
+        </is>
+      </c>
+      <c r="AS1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1123,6 +1129,16 @@
         </is>
       </c>
       <c r="AQ2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AR2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AS2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1260,6 +1276,12 @@
       <c r="AQ3" s="22" t="n">
         <v>4744</v>
       </c>
+      <c r="AR3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS3" s="22" t="n">
+        <v>4776</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1397,6 +1419,12 @@
       <c r="AQ4" s="22" t="n">
         <v>15707</v>
       </c>
+      <c r="AR4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS4" s="22" t="n">
+        <v>15709</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1534,6 +1562,12 @@
       <c r="AQ5" s="22" t="n">
         <v>5264</v>
       </c>
+      <c r="AR5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS5" s="22" t="n">
+        <v>5283</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1671,6 +1705,12 @@
       <c r="AQ6" s="22" t="n">
         <v>6448</v>
       </c>
+      <c r="AR6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS6" s="22" t="n">
+        <v>6467</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1808,6 +1848,12 @@
       <c r="AQ7" s="22" t="n">
         <v>2272</v>
       </c>
+      <c r="AR7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS7" s="22" t="n">
+        <v>2299</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1945,6 +1991,12 @@
       <c r="AQ8" s="22" t="n">
         <v>7201</v>
       </c>
+      <c r="AR8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS8" s="22" t="n">
+        <v>7177</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2082,6 +2134,12 @@
       <c r="AQ9" s="22" t="n">
         <v>3679</v>
       </c>
+      <c r="AR9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS9" s="22" t="n">
+        <v>3696</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2219,6 +2277,12 @@
       <c r="AQ10" s="22" t="n">
         <v>2702</v>
       </c>
+      <c r="AR10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS10" s="22" t="n">
+        <v>2722</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2356,6 +2420,12 @@
       <c r="AQ11" s="22" t="n">
         <v>1032</v>
       </c>
+      <c r="AR11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS11" s="22" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2493,6 +2563,12 @@
       <c r="AQ12" s="22" t="n">
         <v>1097</v>
       </c>
+      <c r="AR12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS12" s="22" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2630,6 +2706,12 @@
       <c r="AQ13" s="22" t="n">
         <v>2178</v>
       </c>
+      <c r="AR13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS13" s="22" t="n">
+        <v>2194</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2767,6 +2849,12 @@
       <c r="AQ14" s="22" t="n">
         <v>2301</v>
       </c>
+      <c r="AR14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS14" s="22" t="n">
+        <v>2308</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2904,6 +2992,12 @@
       <c r="AQ15" s="22" t="n">
         <v>2542</v>
       </c>
+      <c r="AR15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS15" s="22" t="n">
+        <v>2592</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3041,6 +3135,12 @@
       <c r="AQ16" s="22" t="n">
         <v>834</v>
       </c>
+      <c r="AR16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS16" s="22" t="n">
+        <v>838</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3178,6 +3278,12 @@
       <c r="AQ17" s="22" t="n">
         <v>1281</v>
       </c>
+      <c r="AR17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS17" s="22" t="n">
+        <v>1305</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3315,6 +3421,12 @@
       <c r="AQ18" s="22" t="n">
         <v>429</v>
       </c>
+      <c r="AR18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS18" s="22" t="n">
+        <v>435</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3452,6 +3564,12 @@
       <c r="AQ19" s="22" t="n">
         <v>905</v>
       </c>
+      <c r="AR19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS19" s="22" t="n">
+        <v>907</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3589,6 +3707,12 @@
       <c r="AQ20" s="22" t="n">
         <v>1056</v>
       </c>
+      <c r="AR20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS20" s="22" t="n">
+        <v>1069</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3726,6 +3850,12 @@
       <c r="AQ21" s="22" t="n">
         <v>729</v>
       </c>
+      <c r="AR21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS21" s="22" t="n">
+        <v>734</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3863,6 +3993,12 @@
       <c r="AQ22" s="22" t="n">
         <v>620</v>
       </c>
+      <c r="AR22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS22" s="22" t="n">
+        <v>639</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4000,6 +4136,12 @@
       <c r="AQ23" s="22" t="n">
         <v>647</v>
       </c>
+      <c r="AR23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS23" s="22" t="n">
+        <v>680</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -4137,6 +4279,12 @@
       <c r="AQ24" s="22" t="n">
         <v>1418</v>
       </c>
+      <c r="AR24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS24" s="22" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -4274,6 +4422,12 @@
       <c r="AQ25" s="22" t="n">
         <v>605</v>
       </c>
+      <c r="AR25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS25" s="22" t="n">
+        <v>639</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -4411,9 +4565,15 @@
       <c r="AQ26" s="22" t="n">
         <v>302</v>
       </c>
+      <c r="AR26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS26" s="22" t="n">
+        <v>320</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
@@ -4432,6 +4592,7 @@
     <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
   </mergeCells>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS26"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -915,7 +915,13 @@
           <t>26/09/2026</t>
         </is>
       </c>
-      <c r="AS1" s="18" t="n"/>
+      <c r="AS1" s="23" t="n"/>
+      <c r="AT1" s="17" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="AU1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1139,6 +1145,16 @@
         </is>
       </c>
       <c r="AS2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AT2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AU2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1282,6 +1298,12 @@
       <c r="AS3" s="22" t="n">
         <v>4776</v>
       </c>
+      <c r="AT3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU3" s="22" t="n">
+        <v>4803</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1425,6 +1447,12 @@
       <c r="AS4" s="22" t="n">
         <v>15709</v>
       </c>
+      <c r="AT4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU4" s="22" t="n">
+        <v>15705</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1568,6 +1596,12 @@
       <c r="AS5" s="22" t="n">
         <v>5283</v>
       </c>
+      <c r="AT5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU5" s="22" t="n">
+        <v>5326</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1711,6 +1745,12 @@
       <c r="AS6" s="22" t="n">
         <v>6467</v>
       </c>
+      <c r="AT6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU6" s="22" t="n">
+        <v>6472</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1854,6 +1894,12 @@
       <c r="AS7" s="22" t="n">
         <v>2299</v>
       </c>
+      <c r="AT7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU7" s="22" t="n">
+        <v>2316</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1997,6 +2043,12 @@
       <c r="AS8" s="22" t="n">
         <v>7177</v>
       </c>
+      <c r="AT8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU8" s="22" t="n">
+        <v>7149</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2140,6 +2192,12 @@
       <c r="AS9" s="22" t="n">
         <v>3696</v>
       </c>
+      <c r="AT9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU9" s="22" t="n">
+        <v>3704</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2283,6 +2341,12 @@
       <c r="AS10" s="22" t="n">
         <v>2722</v>
       </c>
+      <c r="AT10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU10" s="22" t="n">
+        <v>2720</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2426,6 +2490,12 @@
       <c r="AS11" s="22" t="n">
         <v>1043</v>
       </c>
+      <c r="AT11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU11" s="22" t="n">
+        <v>1045</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2569,6 +2639,12 @@
       <c r="AS12" s="22" t="n">
         <v>1099</v>
       </c>
+      <c r="AT12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU12" s="22" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2712,6 +2788,12 @@
       <c r="AS13" s="22" t="n">
         <v>2194</v>
       </c>
+      <c r="AT13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU13" s="22" t="n">
+        <v>2189</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2855,6 +2937,12 @@
       <c r="AS14" s="22" t="n">
         <v>2308</v>
       </c>
+      <c r="AT14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU14" s="22" t="n">
+        <v>2309</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -2998,6 +3086,12 @@
       <c r="AS15" s="22" t="n">
         <v>2592</v>
       </c>
+      <c r="AT15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU15" s="22" t="n">
+        <v>2634</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3141,6 +3235,12 @@
       <c r="AS16" s="22" t="n">
         <v>838</v>
       </c>
+      <c r="AT16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU16" s="22" t="n">
+        <v>859</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3284,6 +3384,12 @@
       <c r="AS17" s="22" t="n">
         <v>1305</v>
       </c>
+      <c r="AT17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU17" s="22" t="n">
+        <v>1309</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3427,6 +3533,12 @@
       <c r="AS18" s="22" t="n">
         <v>435</v>
       </c>
+      <c r="AT18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU18" s="22" t="n">
+        <v>433</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3570,6 +3682,12 @@
       <c r="AS19" s="22" t="n">
         <v>907</v>
       </c>
+      <c r="AT19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU19" s="22" t="n">
+        <v>907</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3713,6 +3831,12 @@
       <c r="AS20" s="22" t="n">
         <v>1069</v>
       </c>
+      <c r="AT20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU20" s="22" t="n">
+        <v>1075</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3856,6 +3980,12 @@
       <c r="AS21" s="22" t="n">
         <v>734</v>
       </c>
+      <c r="AT21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU21" s="22" t="n">
+        <v>736</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -3999,6 +4129,12 @@
       <c r="AS22" s="22" t="n">
         <v>639</v>
       </c>
+      <c r="AT22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU22" s="22" t="n">
+        <v>648</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4142,6 +4278,12 @@
       <c r="AS23" s="22" t="n">
         <v>680</v>
       </c>
+      <c r="AT23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU23" s="22" t="n">
+        <v>682</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -4285,6 +4427,12 @@
       <c r="AS24" s="22" t="n">
         <v>1428</v>
       </c>
+      <c r="AT24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU24" s="22" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -4428,6 +4576,12 @@
       <c r="AS25" s="22" t="n">
         <v>639</v>
       </c>
+      <c r="AT25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU25" s="22" t="n">
+        <v>651</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -4571,9 +4725,15 @@
       <c r="AS26" s="22" t="n">
         <v>320</v>
       </c>
+      <c r="AT26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU26" s="22" t="n">
+        <v>325</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
@@ -4593,6 +4753,7 @@
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
   </mergeCells>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -921,7 +921,13 @@
           <t>27/09/2026</t>
         </is>
       </c>
-      <c r="AU1" s="18" t="n"/>
+      <c r="AU1" s="23" t="n"/>
+      <c r="AV1" s="17" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="AW1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1155,6 +1161,16 @@
         </is>
       </c>
       <c r="AU2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AV2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AW2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1304,6 +1320,12 @@
       <c r="AU3" s="22" t="n">
         <v>4803</v>
       </c>
+      <c r="AV3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW3" s="22" t="n">
+        <v>4814</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1453,6 +1475,12 @@
       <c r="AU4" s="22" t="n">
         <v>15705</v>
       </c>
+      <c r="AV4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW4" s="22" t="n">
+        <v>15707</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1602,6 +1630,12 @@
       <c r="AU5" s="22" t="n">
         <v>5326</v>
       </c>
+      <c r="AV5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW5" s="22" t="n">
+        <v>5367</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1751,6 +1785,12 @@
       <c r="AU6" s="22" t="n">
         <v>6472</v>
       </c>
+      <c r="AV6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW6" s="22" t="n">
+        <v>6476</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1900,6 +1940,12 @@
       <c r="AU7" s="22" t="n">
         <v>2316</v>
       </c>
+      <c r="AV7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" s="22" t="n">
+        <v>2327</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -2049,6 +2095,12 @@
       <c r="AU8" s="22" t="n">
         <v>7149</v>
       </c>
+      <c r="AV8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW8" s="22" t="n">
+        <v>7133</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2198,6 +2250,12 @@
       <c r="AU9" s="22" t="n">
         <v>3704</v>
       </c>
+      <c r="AV9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW9" s="22" t="n">
+        <v>3714</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2347,6 +2405,12 @@
       <c r="AU10" s="22" t="n">
         <v>2720</v>
       </c>
+      <c r="AV10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW10" s="22" t="n">
+        <v>2719</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2496,6 +2560,12 @@
       <c r="AU11" s="22" t="n">
         <v>1045</v>
       </c>
+      <c r="AV11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW11" s="22" t="n">
+        <v>1052</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2645,6 +2715,12 @@
       <c r="AU12" s="22" t="n">
         <v>1099</v>
       </c>
+      <c r="AV12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW12" s="22" t="n">
+        <v>1102</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2794,6 +2870,12 @@
       <c r="AU13" s="22" t="n">
         <v>2189</v>
       </c>
+      <c r="AV13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW13" s="22" t="n">
+        <v>2172</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -2943,6 +3025,12 @@
       <c r="AU14" s="22" t="n">
         <v>2309</v>
       </c>
+      <c r="AV14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW14" s="22" t="n">
+        <v>2310</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -3092,6 +3180,12 @@
       <c r="AU15" s="22" t="n">
         <v>2634</v>
       </c>
+      <c r="AV15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW15" s="22" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3241,6 +3335,12 @@
       <c r="AU16" s="22" t="n">
         <v>859</v>
       </c>
+      <c r="AV16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW16" s="22" t="n">
+        <v>869</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3390,6 +3490,12 @@
       <c r="AU17" s="22" t="n">
         <v>1309</v>
       </c>
+      <c r="AV17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW17" s="22" t="n">
+        <v>1308</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3539,6 +3645,12 @@
       <c r="AU18" s="22" t="n">
         <v>433</v>
       </c>
+      <c r="AV18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW18" s="22" t="n">
+        <v>431</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3688,6 +3800,12 @@
       <c r="AU19" s="22" t="n">
         <v>907</v>
       </c>
+      <c r="AV19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW19" s="22" t="n">
+        <v>909</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3837,6 +3955,12 @@
       <c r="AU20" s="22" t="n">
         <v>1075</v>
       </c>
+      <c r="AV20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW20" s="22" t="n">
+        <v>1073</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -3986,6 +4110,12 @@
       <c r="AU21" s="22" t="n">
         <v>736</v>
       </c>
+      <c r="AV21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW21" s="22" t="n">
+        <v>745</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -4135,6 +4265,12 @@
       <c r="AU22" s="22" t="n">
         <v>648</v>
       </c>
+      <c r="AV22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW22" s="22" t="n">
+        <v>638</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4284,6 +4420,12 @@
       <c r="AU23" s="22" t="n">
         <v>682</v>
       </c>
+      <c r="AV23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW23" s="22" t="n">
+        <v>685</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -4433,6 +4575,12 @@
       <c r="AU24" s="22" t="n">
         <v>1428</v>
       </c>
+      <c r="AV24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW24" s="22" t="n">
+        <v>1423</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -4582,6 +4730,12 @@
       <c r="AU25" s="22" t="n">
         <v>651</v>
       </c>
+      <c r="AV25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW25" s="22" t="n">
+        <v>665</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -4731,9 +4885,16 @@
       <c r="AU26" s="22" t="n">
         <v>325</v>
       </c>
+      <c r="AV26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW26" s="22" t="n">
+        <v>331</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -927,7 +927,13 @@
           <t>28/09/2026</t>
         </is>
       </c>
-      <c r="AW1" s="18" t="n"/>
+      <c r="AW1" s="23" t="n"/>
+      <c r="AX1" s="17" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="AY1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1171,6 +1177,16 @@
         </is>
       </c>
       <c r="AW2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AX2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="AY2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1326,6 +1342,12 @@
       <c r="AW3" s="22" t="n">
         <v>4814</v>
       </c>
+      <c r="AX3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY3" s="22" t="n">
+        <v>4823</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1481,6 +1503,12 @@
       <c r="AW4" s="22" t="n">
         <v>15707</v>
       </c>
+      <c r="AX4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY4" s="22" t="n">
+        <v>15709</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1636,6 +1664,12 @@
       <c r="AW5" s="22" t="n">
         <v>5367</v>
       </c>
+      <c r="AX5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY5" s="22" t="n">
+        <v>5384</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1791,6 +1825,12 @@
       <c r="AW6" s="22" t="n">
         <v>6476</v>
       </c>
+      <c r="AX6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY6" s="22" t="n">
+        <v>6478</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1946,6 +1986,12 @@
       <c r="AW7" s="22" t="n">
         <v>2327</v>
       </c>
+      <c r="AX7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY7" s="22" t="n">
+        <v>2337</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -2101,6 +2147,12 @@
       <c r="AW8" s="22" t="n">
         <v>7133</v>
       </c>
+      <c r="AX8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY8" s="22" t="n">
+        <v>7146</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2256,6 +2308,12 @@
       <c r="AW9" s="22" t="n">
         <v>3714</v>
       </c>
+      <c r="AX9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY9" s="22" t="n">
+        <v>3723</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2411,6 +2469,12 @@
       <c r="AW10" s="22" t="n">
         <v>2719</v>
       </c>
+      <c r="AX10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY10" s="22" t="n">
+        <v>2716</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2566,6 +2630,12 @@
       <c r="AW11" s="22" t="n">
         <v>1052</v>
       </c>
+      <c r="AX11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY11" s="22" t="n">
+        <v>1058</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2721,6 +2791,12 @@
       <c r="AW12" s="22" t="n">
         <v>1102</v>
       </c>
+      <c r="AX12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY12" s="22" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2876,6 +2952,12 @@
       <c r="AW13" s="22" t="n">
         <v>2172</v>
       </c>
+      <c r="AX13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY13" s="22" t="n">
+        <v>2179</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -3031,6 +3113,12 @@
       <c r="AW14" s="22" t="n">
         <v>2310</v>
       </c>
+      <c r="AX14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY14" s="22" t="n">
+        <v>2345</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -3186,6 +3274,12 @@
       <c r="AW15" s="22" t="n">
         <v>2630</v>
       </c>
+      <c r="AX15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY15" s="22" t="n">
+        <v>2615</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3341,6 +3435,12 @@
       <c r="AW16" s="22" t="n">
         <v>869</v>
       </c>
+      <c r="AX16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY16" s="22" t="n">
+        <v>875</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3496,6 +3596,12 @@
       <c r="AW17" s="22" t="n">
         <v>1308</v>
       </c>
+      <c r="AX17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY17" s="22" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3651,6 +3757,12 @@
       <c r="AW18" s="22" t="n">
         <v>431</v>
       </c>
+      <c r="AX18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY18" s="22" t="n">
+        <v>433</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3806,6 +3918,12 @@
       <c r="AW19" s="22" t="n">
         <v>909</v>
       </c>
+      <c r="AX19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY19" s="22" t="n">
+        <v>912</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -3961,6 +4079,12 @@
       <c r="AW20" s="22" t="n">
         <v>1073</v>
       </c>
+      <c r="AX20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY20" s="22" t="n">
+        <v>1080</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -4116,6 +4240,12 @@
       <c r="AW21" s="22" t="n">
         <v>745</v>
       </c>
+      <c r="AX21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY21" s="22" t="n">
+        <v>751</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -4271,6 +4401,12 @@
       <c r="AW22" s="22" t="n">
         <v>638</v>
       </c>
+      <c r="AX22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY22" s="22" t="n">
+        <v>637</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4426,6 +4562,12 @@
       <c r="AW23" s="22" t="n">
         <v>685</v>
       </c>
+      <c r="AX23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY23" s="22" t="n">
+        <v>685</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -4581,6 +4723,12 @@
       <c r="AW24" s="22" t="n">
         <v>1423</v>
       </c>
+      <c r="AX24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY24" s="22" t="n">
+        <v>1423</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -4736,6 +4884,12 @@
       <c r="AW25" s="22" t="n">
         <v>665</v>
       </c>
+      <c r="AX25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY25" s="22" t="n">
+        <v>665</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -4891,10 +5045,17 @@
       <c r="AW26" s="22" t="n">
         <v>331</v>
       </c>
+      <c r="AX26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY26" s="22" t="n">
+        <v>338</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:BA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -933,7 +933,13 @@
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="AY1" s="18" t="n"/>
+      <c r="AY1" s="23" t="n"/>
+      <c r="AZ1" s="17" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="BA1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1187,6 +1193,16 @@
         </is>
       </c>
       <c r="AY2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="AZ2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="BA2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1348,6 +1364,12 @@
       <c r="AY3" s="22" t="n">
         <v>4823</v>
       </c>
+      <c r="AZ3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA3" s="22" t="n">
+        <v>4833</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1509,6 +1531,12 @@
       <c r="AY4" s="22" t="n">
         <v>15709</v>
       </c>
+      <c r="AZ4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA4" s="22" t="n">
+        <v>15718</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1670,6 +1698,12 @@
       <c r="AY5" s="22" t="n">
         <v>5384</v>
       </c>
+      <c r="AZ5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA5" s="22" t="n">
+        <v>5418</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1831,6 +1865,12 @@
       <c r="AY6" s="22" t="n">
         <v>6478</v>
       </c>
+      <c r="AZ6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA6" s="22" t="n">
+        <v>6503</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1992,6 +2032,12 @@
       <c r="AY7" s="22" t="n">
         <v>2337</v>
       </c>
+      <c r="AZ7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA7" s="22" t="n">
+        <v>2358</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -2153,6 +2199,12 @@
       <c r="AY8" s="22" t="n">
         <v>7146</v>
       </c>
+      <c r="AZ8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA8" s="22" t="n">
+        <v>7149</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2314,6 +2366,12 @@
       <c r="AY9" s="22" t="n">
         <v>3723</v>
       </c>
+      <c r="AZ9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA9" s="22" t="n">
+        <v>3660</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2475,6 +2533,12 @@
       <c r="AY10" s="22" t="n">
         <v>2716</v>
       </c>
+      <c r="AZ10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA10" s="22" t="n">
+        <v>2728</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2636,6 +2700,12 @@
       <c r="AY11" s="22" t="n">
         <v>1058</v>
       </c>
+      <c r="AZ11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA11" s="22" t="n">
+        <v>1071</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2797,6 +2867,12 @@
       <c r="AY12" s="22" t="n">
         <v>1108</v>
       </c>
+      <c r="AZ12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA12" s="22" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -2958,6 +3034,12 @@
       <c r="AY13" s="22" t="n">
         <v>2179</v>
       </c>
+      <c r="AZ13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA13" s="22" t="n">
+        <v>2176</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -3119,6 +3201,12 @@
       <c r="AY14" s="22" t="n">
         <v>2345</v>
       </c>
+      <c r="AZ14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA14" s="22" t="n">
+        <v>2369</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -3280,6 +3368,12 @@
       <c r="AY15" s="22" t="n">
         <v>2615</v>
       </c>
+      <c r="AZ15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA15" s="22" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3441,6 +3535,12 @@
       <c r="AY16" s="22" t="n">
         <v>875</v>
       </c>
+      <c r="AZ16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA16" s="22" t="n">
+        <v>876</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3602,6 +3702,12 @@
       <c r="AY17" s="22" t="n">
         <v>1325</v>
       </c>
+      <c r="AZ17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA17" s="22" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3763,6 +3869,12 @@
       <c r="AY18" s="22" t="n">
         <v>433</v>
       </c>
+      <c r="AZ18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA18" s="22" t="n">
+        <v>434</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -3924,6 +4036,12 @@
       <c r="AY19" s="22" t="n">
         <v>912</v>
       </c>
+      <c r="AZ19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA19" s="22" t="n">
+        <v>916</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -4085,6 +4203,12 @@
       <c r="AY20" s="22" t="n">
         <v>1080</v>
       </c>
+      <c r="AZ20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA20" s="22" t="n">
+        <v>1080</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -4246,6 +4370,12 @@
       <c r="AY21" s="22" t="n">
         <v>751</v>
       </c>
+      <c r="AZ21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA21" s="22" t="n">
+        <v>761</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -4407,6 +4537,12 @@
       <c r="AY22" s="22" t="n">
         <v>637</v>
       </c>
+      <c r="AZ22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA22" s="22" t="n">
+        <v>638</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4568,6 +4704,12 @@
       <c r="AY23" s="22" t="n">
         <v>685</v>
       </c>
+      <c r="AZ23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA23" s="22" t="n">
+        <v>690</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -4729,6 +4871,12 @@
       <c r="AY24" s="22" t="n">
         <v>1423</v>
       </c>
+      <c r="AZ24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA24" s="22" t="n">
+        <v>1423</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -4890,6 +5038,12 @@
       <c r="AY25" s="22" t="n">
         <v>665</v>
       </c>
+      <c r="AZ25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA25" s="22" t="n">
+        <v>669</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -5051,12 +5205,19 @@
       <c r="AY26" s="22" t="n">
         <v>338</v>
       </c>
+      <c r="AZ26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA26" s="22" t="n">
+        <v>338</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA26"/>
+  <dimension ref="A1:BC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -939,7 +939,13 @@
           <t>30/09/2026</t>
         </is>
       </c>
-      <c r="BA1" s="18" t="n"/>
+      <c r="BA1" s="23" t="n"/>
+      <c r="BB1" s="17" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="BC1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1203,6 +1209,16 @@
         </is>
       </c>
       <c r="BA2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="BB2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="BC2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1370,6 +1386,12 @@
       <c r="BA3" s="22" t="n">
         <v>4833</v>
       </c>
+      <c r="BB3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" s="22" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1537,6 +1559,12 @@
       <c r="BA4" s="22" t="n">
         <v>15718</v>
       </c>
+      <c r="BB4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC4" s="22" t="n">
+        <v>15742</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1704,6 +1732,12 @@
       <c r="BA5" s="22" t="n">
         <v>5418</v>
       </c>
+      <c r="BB5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC5" s="22" t="n">
+        <v>5442</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1871,6 +1905,12 @@
       <c r="BA6" s="22" t="n">
         <v>6503</v>
       </c>
+      <c r="BB6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC6" s="22" t="n">
+        <v>6526</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -2038,6 +2078,12 @@
       <c r="BA7" s="22" t="n">
         <v>2358</v>
       </c>
+      <c r="BB7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC7" s="22" t="n">
+        <v>2367</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -2205,6 +2251,12 @@
       <c r="BA8" s="22" t="n">
         <v>7149</v>
       </c>
+      <c r="BB8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC8" s="22" t="n">
+        <v>7157</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2372,6 +2424,12 @@
       <c r="BA9" s="22" t="n">
         <v>3660</v>
       </c>
+      <c r="BB9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC9" s="22" t="n">
+        <v>3668</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2539,6 +2597,12 @@
       <c r="BA10" s="22" t="n">
         <v>2728</v>
       </c>
+      <c r="BB10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC10" s="22" t="n">
+        <v>2742</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2706,6 +2770,12 @@
       <c r="BA11" s="22" t="n">
         <v>1071</v>
       </c>
+      <c r="BB11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC11" s="22" t="n">
+        <v>1078</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2873,6 +2943,12 @@
       <c r="BA12" s="22" t="n">
         <v>1108</v>
       </c>
+      <c r="BB12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC12" s="22" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -3040,6 +3116,12 @@
       <c r="BA13" s="22" t="n">
         <v>2176</v>
       </c>
+      <c r="BB13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC13" s="22" t="n">
+        <v>2205</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -3207,6 +3289,12 @@
       <c r="BA14" s="22" t="n">
         <v>2369</v>
       </c>
+      <c r="BB14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC14" s="22" t="n">
+        <v>2371</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -3374,6 +3462,12 @@
       <c r="BA15" s="22" t="n">
         <v>2588</v>
       </c>
+      <c r="BB15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC15" s="22" t="n">
+        <v>2586</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3541,6 +3635,12 @@
       <c r="BA16" s="22" t="n">
         <v>876</v>
       </c>
+      <c r="BB16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC16" s="22" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3708,6 +3808,12 @@
       <c r="BA17" s="22" t="n">
         <v>1325</v>
       </c>
+      <c r="BB17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC17" s="22" t="n">
+        <v>1314</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3875,6 +3981,12 @@
       <c r="BA18" s="22" t="n">
         <v>434</v>
       </c>
+      <c r="BB18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC18" s="22" t="n">
+        <v>435</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -4042,6 +4154,12 @@
       <c r="BA19" s="22" t="n">
         <v>916</v>
       </c>
+      <c r="BB19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC19" s="22" t="n">
+        <v>924</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -4209,6 +4327,12 @@
       <c r="BA20" s="22" t="n">
         <v>1080</v>
       </c>
+      <c r="BB20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" s="22" t="n">
+        <v>1083</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -4376,6 +4500,12 @@
       <c r="BA21" s="22" t="n">
         <v>761</v>
       </c>
+      <c r="BB21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC21" s="22" t="n">
+        <v>767</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -4543,6 +4673,12 @@
       <c r="BA22" s="22" t="n">
         <v>638</v>
       </c>
+      <c r="BB22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC22" s="22" t="n">
+        <v>639</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4710,6 +4846,12 @@
       <c r="BA23" s="22" t="n">
         <v>690</v>
       </c>
+      <c r="BB23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC23" s="22" t="n">
+        <v>693</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -4877,6 +5019,12 @@
       <c r="BA24" s="22" t="n">
         <v>1423</v>
       </c>
+      <c r="BB24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC24" s="22" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -5044,6 +5192,12 @@
       <c r="BA25" s="22" t="n">
         <v>669</v>
       </c>
+      <c r="BB25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC25" s="22" t="n">
+        <v>673</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -5211,9 +5365,15 @@
       <c r="BA26" s="22" t="n">
         <v>338</v>
       </c>
+      <c r="BB26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC26" s="22" t="n">
+        <v>339</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="H1:I1"/>
@@ -5229,6 +5389,7 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="T1:U1"/>
+    <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="X1:Y1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC26"/>
+  <dimension ref="A1:BE26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -945,7 +945,13 @@
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="BC1" s="18" t="n"/>
+      <c r="BC1" s="23" t="n"/>
+      <c r="BD1" s="17" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="BE1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1219,6 +1225,16 @@
         </is>
       </c>
       <c r="BC2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="BD2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="BE2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1392,6 +1408,12 @@
       <c r="BC3" s="22" t="n">
         <v>4836</v>
       </c>
+      <c r="BD3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE3" s="22" t="n">
+        <v>4842</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1565,6 +1587,12 @@
       <c r="BC4" s="22" t="n">
         <v>15742</v>
       </c>
+      <c r="BD4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE4" s="22" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1738,6 +1766,12 @@
       <c r="BC5" s="22" t="n">
         <v>5442</v>
       </c>
+      <c r="BD5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE5" s="22" t="n">
+        <v>5465</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1911,6 +1945,12 @@
       <c r="BC6" s="22" t="n">
         <v>6526</v>
       </c>
+      <c r="BD6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE6" s="22" t="n">
+        <v>6543</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -2084,6 +2124,12 @@
       <c r="BC7" s="22" t="n">
         <v>2367</v>
       </c>
+      <c r="BD7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE7" s="22" t="n">
+        <v>2390</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -2257,6 +2303,12 @@
       <c r="BC8" s="22" t="n">
         <v>7157</v>
       </c>
+      <c r="BD8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE8" s="22" t="n">
+        <v>7171</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2430,6 +2482,12 @@
       <c r="BC9" s="22" t="n">
         <v>3668</v>
       </c>
+      <c r="BD9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE9" s="22" t="n">
+        <v>3673</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2603,6 +2661,12 @@
       <c r="BC10" s="22" t="n">
         <v>2742</v>
       </c>
+      <c r="BD10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE10" s="22" t="n">
+        <v>2746</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2776,6 +2840,12 @@
       <c r="BC11" s="22" t="n">
         <v>1078</v>
       </c>
+      <c r="BD11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE11" s="22" t="n">
+        <v>1078</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -2949,6 +3019,12 @@
       <c r="BC12" s="22" t="n">
         <v>1108</v>
       </c>
+      <c r="BD12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE12" s="22" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -3122,6 +3198,12 @@
       <c r="BC13" s="22" t="n">
         <v>2205</v>
       </c>
+      <c r="BD13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE13" s="22" t="n">
+        <v>2210</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -3295,6 +3377,12 @@
       <c r="BC14" s="22" t="n">
         <v>2371</v>
       </c>
+      <c r="BD14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE14" s="22" t="n">
+        <v>2374</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -3468,6 +3556,12 @@
       <c r="BC15" s="22" t="n">
         <v>2586</v>
       </c>
+      <c r="BD15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE15" s="22" t="n">
+        <v>2592</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3641,6 +3735,12 @@
       <c r="BC16" s="22" t="n">
         <v>878</v>
       </c>
+      <c r="BD16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE16" s="22" t="n">
+        <v>879</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3814,6 +3914,12 @@
       <c r="BC17" s="22" t="n">
         <v>1314</v>
       </c>
+      <c r="BD17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE17" s="22" t="n">
+        <v>1321</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -3987,6 +4093,12 @@
       <c r="BC18" s="22" t="n">
         <v>435</v>
       </c>
+      <c r="BD18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE18" s="22" t="n">
+        <v>435</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -4160,6 +4272,12 @@
       <c r="BC19" s="22" t="n">
         <v>924</v>
       </c>
+      <c r="BD19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE19" s="22" t="n">
+        <v>926</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -4333,6 +4451,12 @@
       <c r="BC20" s="22" t="n">
         <v>1083</v>
       </c>
+      <c r="BD20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE20" s="22" t="n">
+        <v>1085</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -4506,6 +4630,12 @@
       <c r="BC21" s="22" t="n">
         <v>767</v>
       </c>
+      <c r="BD21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE21" s="22" t="n">
+        <v>772</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -4679,6 +4809,12 @@
       <c r="BC22" s="22" t="n">
         <v>639</v>
       </c>
+      <c r="BD22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE22" s="22" t="n">
+        <v>642</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4852,6 +4988,12 @@
       <c r="BC23" s="22" t="n">
         <v>693</v>
       </c>
+      <c r="BD23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE23" s="22" t="n">
+        <v>694</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -5025,6 +5167,12 @@
       <c r="BC24" s="22" t="n">
         <v>1424</v>
       </c>
+      <c r="BD24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE24" s="22" t="n">
+        <v>1432</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -5198,6 +5346,12 @@
       <c r="BC25" s="22" t="n">
         <v>673</v>
       </c>
+      <c r="BD25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE25" s="22" t="n">
+        <v>685</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -5371,9 +5525,15 @@
       <c r="BC26" s="22" t="n">
         <v>339</v>
       </c>
+      <c r="BD26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE26" s="22" t="n">
+        <v>345</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="H1:I1"/>
@@ -5391,6 +5551,7 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="L1:M1"/>
+    <mergeCell ref="BD1:BE1"/>
     <mergeCell ref="AF1:AG1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="AJ1:AK1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE26"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -951,7 +951,13 @@
           <t>02/10/2026</t>
         </is>
       </c>
-      <c r="BE1" s="18" t="n"/>
+      <c r="BE1" s="23" t="n"/>
+      <c r="BF1" s="17" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="BG1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -1235,6 +1241,16 @@
         </is>
       </c>
       <c r="BE2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="BF2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="BG2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1414,6 +1430,12 @@
       <c r="BE3" s="22" t="n">
         <v>4842</v>
       </c>
+      <c r="BF3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG3" s="22" t="n">
+        <v>4844</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1593,6 +1615,12 @@
       <c r="BE4" s="22" t="n">
         <v>15765</v>
       </c>
+      <c r="BF4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG4" s="22" t="n">
+        <v>15777</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1772,6 +1800,12 @@
       <c r="BE5" s="22" t="n">
         <v>5465</v>
       </c>
+      <c r="BF5" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG5" s="22" t="n">
+        <v>5482</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1951,6 +1985,12 @@
       <c r="BE6" s="22" t="n">
         <v>6543</v>
       </c>
+      <c r="BF6" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG6" s="22" t="n">
+        <v>6554</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -2130,6 +2170,12 @@
       <c r="BE7" s="22" t="n">
         <v>2390</v>
       </c>
+      <c r="BF7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG7" s="22" t="n">
+        <v>2388</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -2309,6 +2355,12 @@
       <c r="BE8" s="22" t="n">
         <v>7171</v>
       </c>
+      <c r="BF8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG8" s="22" t="n">
+        <v>7178</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -2488,6 +2540,12 @@
       <c r="BE9" s="22" t="n">
         <v>3673</v>
       </c>
+      <c r="BF9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG9" s="22" t="n">
+        <v>3658</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -2667,6 +2725,12 @@
       <c r="BE10" s="22" t="n">
         <v>2746</v>
       </c>
+      <c r="BF10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG10" s="22" t="n">
+        <v>2755</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -2846,6 +2910,12 @@
       <c r="BE11" s="22" t="n">
         <v>1078</v>
       </c>
+      <c r="BF11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG11" s="22" t="n">
+        <v>1081</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -3025,6 +3095,12 @@
       <c r="BE12" s="22" t="n">
         <v>1108</v>
       </c>
+      <c r="BF12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG12" s="22" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -3204,6 +3280,12 @@
       <c r="BE13" s="22" t="n">
         <v>2210</v>
       </c>
+      <c r="BF13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG13" s="22" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -3383,6 +3465,12 @@
       <c r="BE14" s="22" t="n">
         <v>2374</v>
       </c>
+      <c r="BF14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG14" s="22" t="n">
+        <v>2376</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -3562,6 +3650,12 @@
       <c r="BE15" s="22" t="n">
         <v>2592</v>
       </c>
+      <c r="BF15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG15" s="22" t="n">
+        <v>2582</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -3741,6 +3835,12 @@
       <c r="BE16" s="22" t="n">
         <v>879</v>
       </c>
+      <c r="BF16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG16" s="22" t="n">
+        <v>881</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -3920,6 +4020,12 @@
       <c r="BE17" s="22" t="n">
         <v>1321</v>
       </c>
+      <c r="BF17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG17" s="22" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -4099,6 +4205,12 @@
       <c r="BE18" s="22" t="n">
         <v>435</v>
       </c>
+      <c r="BF18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG18" s="22" t="n">
+        <v>438</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -4278,6 +4390,12 @@
       <c r="BE19" s="22" t="n">
         <v>926</v>
       </c>
+      <c r="BF19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG19" s="22" t="n">
+        <v>938</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -4457,6 +4575,12 @@
       <c r="BE20" s="22" t="n">
         <v>1085</v>
       </c>
+      <c r="BF20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG20" s="22" t="n">
+        <v>1089</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -4636,6 +4760,12 @@
       <c r="BE21" s="22" t="n">
         <v>772</v>
       </c>
+      <c r="BF21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG21" s="22" t="n">
+        <v>784</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -4815,6 +4945,12 @@
       <c r="BE22" s="22" t="n">
         <v>642</v>
       </c>
+      <c r="BF22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG22" s="22" t="n">
+        <v>650</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -4994,6 +5130,12 @@
       <c r="BE23" s="22" t="n">
         <v>694</v>
       </c>
+      <c r="BF23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG23" s="22" t="n">
+        <v>701</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -5173,6 +5315,12 @@
       <c r="BE24" s="22" t="n">
         <v>1432</v>
       </c>
+      <c r="BF24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG24" s="22" t="n">
+        <v>1434</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -5352,6 +5500,12 @@
       <c r="BE25" s="22" t="n">
         <v>685</v>
       </c>
+      <c r="BF25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG25" s="22" t="n">
+        <v>689</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -5531,9 +5685,15 @@
       <c r="BE26" s="22" t="n">
         <v>345</v>
       </c>
+      <c r="BF26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG26" s="22" t="n">
+        <v>346</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="H1:I1"/>
@@ -5547,6 +5707,7 @@
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="BF1:BG1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="BB1:BC1"/>
